--- a/data/trans_dic/P19C03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 24,85</t>
+          <t>18,25; 24,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,26</t>
+          <t>16,59; 22,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,73</t>
+          <t>16,7; 24,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,08</t>
+          <t>11,93; 17,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,0; 25,58</t>
+          <t>20,18; 25,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,4; 26,5</t>
+          <t>21,13; 26,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,64</t>
+          <t>19,36; 25,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,93</t>
+          <t>12,67; 16,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,19; 24,36</t>
+          <t>20,2; 24,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,14; 23,89</t>
+          <t>20,2; 24,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 24,28</t>
+          <t>18,89; 23,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,6</t>
+          <t>12,83; 16,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,8; 40,41</t>
+          <t>35,06; 40,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,34; 37,09</t>
+          <t>32,03; 37,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,56</t>
+          <t>28,05; 32,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 22,04</t>
+          <t>13,26; 22,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,32; 41,39</t>
+          <t>35,89; 41,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 35,83</t>
+          <t>31,26; 36,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,9; 31,4</t>
+          <t>26,76; 31,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 22,01</t>
+          <t>13,52; 21,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 40,02</t>
+          <t>36,37; 40,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 35,68</t>
+          <t>32,39; 35,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,06; 31,43</t>
+          <t>27,95; 31,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 21,31</t>
+          <t>15,14; 21,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 36,41</t>
+          <t>27,17; 36,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 37,35</t>
+          <t>27,69; 36,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 29,69</t>
+          <t>21,09; 29,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 20,21</t>
+          <t>13,78; 20,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 36,76</t>
+          <t>26,84; 36,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,19; 30,95</t>
+          <t>21,76; 31,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 25,42</t>
+          <t>18,4; 25,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 21,14</t>
+          <t>15,98; 20,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,56; 35,19</t>
+          <t>28,38; 34,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 32,76</t>
+          <t>25,99; 32,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,77; 26,49</t>
+          <t>21,2; 26,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 19,72</t>
+          <t>15,62; 19,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,08; 34,04</t>
+          <t>30,09; 33,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,34; 31,82</t>
+          <t>28,45; 31,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,8; 29,27</t>
+          <t>25,93; 29,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,24</t>
+          <t>13,71; 20,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,12; 33,87</t>
+          <t>30,36; 33,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 30,72</t>
+          <t>27,3; 30,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 27,76</t>
+          <t>24,54; 27,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 20,03</t>
+          <t>14,81; 20,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,28</t>
+          <t>30,82; 33,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,33; 30,79</t>
+          <t>28,31; 30,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,65; 28,03</t>
+          <t>25,66; 28,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 19,4</t>
+          <t>15,36; 19,48</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>126944; 171044</t>
+          <t>125603; 169626</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129076; 173246</t>
+          <t>129084; 174337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75363; 108562</t>
+          <t>76402; 110573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57629; 87397</t>
+          <t>57664; 86944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>191758; 245324</t>
+          <t>193488; 245701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>241465; 299045</t>
+          <t>238453; 297879</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119787; 163792</t>
+          <t>123691; 163644</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90198; 122150</t>
+          <t>91433; 121682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>332507; 401227</t>
+          <t>332736; 398954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>383989; 455471</t>
+          <t>385045; 461486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209407; 266180</t>
+          <t>207077; 258808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>157248; 200022</t>
+          <t>154606; 199094</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>457407; 531189</t>
+          <t>460849; 531679</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>545422; 625489</t>
+          <t>540199; 623988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>478885; 552452</t>
+          <t>475979; 554586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>282457; 491711</t>
+          <t>295770; 495897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>498746; 568307</t>
+          <t>492907; 568958</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>494887; 569760</t>
+          <t>497157; 576779</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>459722; 536603</t>
+          <t>457239; 531074</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>293891; 483672</t>
+          <t>297009; 478431</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>977621; 1075721</t>
+          <t>977389; 1078371</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1061305; 1169035</t>
+          <t>1061373; 1172656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>955569; 1070139</t>
+          <t>951845; 1062309</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>655542; 943621</t>
+          <t>670396; 945230</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>125246; 164205</t>
+          <t>122506; 163090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>121853; 165134</t>
+          <t>122420; 162598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105618; 148223</t>
+          <t>105268; 145355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86514; 127618</t>
+          <t>86986; 128196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>111916; 150261</t>
+          <t>109718; 147397</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93595; 130538</t>
+          <t>91778; 131144</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93023; 129195</t>
+          <t>93524; 130325</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>103978; 137724</t>
+          <t>104154; 136708</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245507; 302551</t>
+          <t>243975; 300164</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>227364; 283029</t>
+          <t>224530; 282327</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209240; 266876</t>
+          <t>213592; 267601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>198807; 252999</t>
+          <t>200391; 253754</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>738000; 835283</t>
+          <t>738252; 831122</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>823753; 924825</t>
+          <t>826881; 927212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>684457; 776562</t>
+          <t>687976; 783656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>456793; 677103</t>
+          <t>458468; 675248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>825485; 928483</t>
+          <t>832173; 926843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>861144; 964626</t>
+          <t>857377; 964574</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>697129; 792775</t>
+          <t>700814; 791991</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>510788; 715269</t>
+          <t>528827; 714965</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1595910; 1728616</t>
+          <t>1600758; 1731109</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1713472; 1861730</t>
+          <t>1711695; 1860171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1413050; 1544474</t>
+          <t>1413411; 1549998</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1069274; 1341860</t>
+          <t>1062306; 1347249</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,25; 24,64</t>
+          <t>18,26; 24,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,4</t>
+          <t>16,79; 22,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 24,17</t>
+          <t>16,2; 23,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 17,99</t>
+          <t>12,2; 19,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,18; 25,62</t>
+          <t>20,33; 25,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,13; 26,4</t>
+          <t>21,33; 26,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 25,61</t>
+          <t>18,99; 25,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 16,86</t>
+          <t>12,65; 16,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 24,22</t>
+          <t>20,19; 24,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 24,21</t>
+          <t>19,77; 23,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,89; 23,61</t>
+          <t>18,83; 23,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,83; 16,52</t>
+          <t>13,29; 16,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 40,45</t>
+          <t>35,02; 40,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,03; 37,0</t>
+          <t>31,97; 36,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,05; 32,69</t>
+          <t>28,12; 32,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,23</t>
+          <t>19,02; 23,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 41,43</t>
+          <t>36,2; 41,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,26; 36,27</t>
+          <t>31,05; 35,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,76; 31,08</t>
+          <t>26,88; 31,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 21,77</t>
+          <t>17,73; 21,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 40,12</t>
+          <t>36,3; 39,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 35,79</t>
+          <t>32,27; 35,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 31,2</t>
+          <t>28,06; 31,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,35</t>
+          <t>19,0; 21,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,17; 36,17</t>
+          <t>27,05; 36,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,69; 36,78</t>
+          <t>27,33; 36,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,09; 29,11</t>
+          <t>21,55; 29,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,78; 20,31</t>
+          <t>13,18; 19,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,84; 36,06</t>
+          <t>27,17; 36,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 31,09</t>
+          <t>21,62; 30,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,4; 25,64</t>
+          <t>18,5; 25,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 20,98</t>
+          <t>16,93; 22,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,38; 34,91</t>
+          <t>28,61; 35,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,99; 32,68</t>
+          <t>26,07; 32,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,2; 26,56</t>
+          <t>20,95; 26,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,62; 19,78</t>
+          <t>15,92; 19,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,09; 33,87</t>
+          <t>30,02; 33,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,45; 31,9</t>
+          <t>28,38; 31,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,93; 29,54</t>
+          <t>25,93; 29,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 20,19</t>
+          <t>17,6; 20,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,36; 33,81</t>
+          <t>30,17; 33,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,71</t>
+          <t>27,61; 30,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,73</t>
+          <t>24,58; 27,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 20,02</t>
+          <t>17,18; 19,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 33,32</t>
+          <t>30,61; 33,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,76</t>
+          <t>28,38; 30,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 28,13</t>
+          <t>25,85; 28,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 19,48</t>
+          <t>17,8; 19,68</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>197769</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>125603; 169626</t>
+          <t>125668; 168534</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129084; 174337</t>
+          <t>130689; 174607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76402; 110573</t>
+          <t>74123; 108930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57664; 86944</t>
+          <t>65401; 102146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>193488; 245701</t>
+          <t>194924; 245564</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>238453; 297879</t>
+          <t>240651; 297482</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>123691; 163644</t>
+          <t>121329; 163984</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91433; 121682</t>
+          <t>99253; 131553</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>332736; 398954</t>
+          <t>332537; 397955</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385045; 461486</t>
+          <t>376866; 455072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207077; 258808</t>
+          <t>206479; 259738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>154606; 199094</t>
+          <t>175551; 223131</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423516</t>
+          <t>452081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>399063</t>
+          <t>407658</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>822579</t>
+          <t>859738</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>460849; 531679</t>
+          <t>460285; 528399</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>540199; 623988</t>
+          <t>539218; 619716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>475979; 554586</t>
+          <t>477050; 551520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295770; 495897</t>
+          <t>408276; 499476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>492907; 568958</t>
+          <t>497057; 567908</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>497157; 576779</t>
+          <t>493768; 571975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>457239; 531074</t>
+          <t>459322; 533514</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>297009; 478431</t>
+          <t>374159; 446490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>977389; 1078371</t>
+          <t>975683; 1073008</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1061373; 1172656</t>
+          <t>1057308; 1167344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>951845; 1062309</t>
+          <t>955675; 1064105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>670396; 945230</t>
+          <t>808770; 924217</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106157</t>
+          <t>112711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>119566</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>225723</t>
+          <t>254302</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>122506; 163090</t>
+          <t>121973; 164563</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122420; 162598</t>
+          <t>120848; 162374</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105268; 145355</t>
+          <t>107596; 146932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86986; 128196</t>
+          <t>92471; 136019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>109718; 147397</t>
+          <t>111085; 149174</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91778; 131144</t>
+          <t>91209; 130086</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93524; 130325</t>
+          <t>94049; 129195</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>104154; 136708</t>
+          <t>122617; 161010</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243975; 300164</t>
+          <t>245937; 301506</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224530; 282327</t>
+          <t>225267; 281675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>213592; 267601</t>
+          <t>211112; 264351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>200391; 253754</t>
+          <t>227043; 285152</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601529</t>
+          <t>648446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>623530</t>
+          <t>663364</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1225059</t>
+          <t>1311809</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>738252; 831122</t>
+          <t>736551; 833872</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>826881; 927212</t>
+          <t>825074; 927386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>687976; 783656</t>
+          <t>687880; 781787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>458468; 675248</t>
+          <t>595507; 702634</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>832173; 926843</t>
+          <t>826844; 928824</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>857377; 964574</t>
+          <t>867097; 968905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>700814; 791991</t>
+          <t>702111; 795219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>528827; 714965</t>
+          <t>621785; 706839</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1600758; 1731109</t>
+          <t>1590088; 1727432</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1711695; 1860171</t>
+          <t>1716379; 1860138</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1413411; 1549998</t>
+          <t>1424152; 1551894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1062306; 1347249</t>
+          <t>1246410; 1378326</t>
         </is>
       </c>
     </row>
